--- a/data/controles_results/dif_medias/controls_staggered_vars/difmedias_controles_staggered_variables_2019_T3_0.xlsx
+++ b/data/controles_results/dif_medias/controls_staggered_vars/difmedias_controles_staggered_variables_2019_T3_0.xlsx
@@ -45,7 +45,7 @@
     <t>N</t>
   </si>
   <si>
-    <t>81</t>
+    <t>75</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -57,40 +57,40 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>0.321</t>
-  </si>
-  <si>
-    <t>(0.052)</t>
-  </si>
-  <si>
-    <t>0.444</t>
-  </si>
-  <si>
-    <t>(0.056)</t>
-  </si>
-  <si>
-    <t>0.272</t>
-  </si>
-  <si>
-    <t>(0.050)</t>
-  </si>
-  <si>
-    <t>0.975</t>
-  </si>
-  <si>
-    <t>(0.303)</t>
-  </si>
-  <si>
-    <t>1.123</t>
-  </si>
-  <si>
-    <t>(0.184)</t>
-  </si>
-  <si>
-    <t>0.407</t>
-  </si>
-  <si>
-    <t>(0.089)</t>
+    <t>0.347</t>
+  </si>
+  <si>
+    <t>(0.055)</t>
+  </si>
+  <si>
+    <t>0.480</t>
+  </si>
+  <si>
+    <t>(0.058)</t>
+  </si>
+  <si>
+    <t>0.293</t>
+  </si>
+  <si>
+    <t>(0.053)</t>
+  </si>
+  <si>
+    <t>1.053</t>
+  </si>
+  <si>
+    <t>(0.326)</t>
+  </si>
+  <si>
+    <t>1.213</t>
+  </si>
+  <si>
+    <t>(0.195)</t>
+  </si>
+  <si>
+    <t>0.440</t>
+  </si>
+  <si>
+    <t>(0.095)</t>
   </si>
   <si>
     <t>35</t>
@@ -138,7 +138,7 @@
     <t>(0.273)</t>
   </si>
   <si>
-    <t>116</t>
+    <t>110</t>
   </si>
   <si>
     <t>(2)-(1)</t>
@@ -150,22 +150,22 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>0.193**</t>
-  </si>
-  <si>
-    <t>0.356***</t>
-  </si>
-  <si>
-    <t>0.386***</t>
-  </si>
-  <si>
-    <t>1.168</t>
-  </si>
-  <si>
-    <t>2.162***</t>
-  </si>
-  <si>
-    <t>1.135***</t>
+    <t>0.168*</t>
+  </si>
+  <si>
+    <t>0.320***</t>
+  </si>
+  <si>
+    <t>0.364***</t>
+  </si>
+  <si>
+    <t>1.090</t>
+  </si>
+  <si>
+    <t>2.072***</t>
+  </si>
+  <si>
+    <t>1.103***</t>
   </si>
 </sst>
 </file>
